--- a/AAII_Financials/Quarterly/MLYBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MLYBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
   <si>
     <t>MLYBY</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,56 +656,59 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -733,8 +736,11 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -762,8 +768,11 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -791,8 +800,11 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -804,8 +816,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -833,8 +846,11 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -862,8 +878,11 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -891,8 +910,11 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -920,8 +942,11 @@
       <c r="K15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -930,8 +955,9 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -959,8 +985,11 @@
       <c r="K17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -988,8 +1017,11 @@
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1001,8 +1033,9 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1030,8 +1063,11 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1059,8 +1095,11 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1088,8 +1127,11 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1117,8 +1159,11 @@
       <c r="K23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1146,8 +1191,11 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1175,8 +1223,11 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1204,8 +1255,11 @@
       <c r="K26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1233,8 +1287,11 @@
       <c r="K27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1262,8 +1319,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1291,8 +1351,11 @@
       <c r="K29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1320,8 +1383,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1349,8 +1415,11 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1378,8 +1447,11 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1407,8 +1479,11 @@
       <c r="K33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1436,8 +1511,11 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1465,42 +1543,48 @@
       <c r="K35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1512,8 +1596,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1525,269 +1610,297 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9062800</v>
+      </c>
+      <c r="E41" s="3">
         <v>8612800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6379400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8018100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6300600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7890400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7227400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6365400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8578500</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>24272900</v>
+      </c>
+      <c r="E42" s="3">
         <v>24300200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>22771900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>21920100</v>
       </c>
-      <c r="G42" s="3">
-        <v>22740500</v>
-      </c>
       <c r="H42" s="3">
+        <v>22193500</v>
+      </c>
+      <c r="I42" s="3">
         <v>19915800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>22011000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>24379500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>21721100</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3133400</v>
+      </c>
+      <c r="E43" s="3">
         <v>5903300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3578300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2736400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2300400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4297500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3409100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3278100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2296900</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>85100</v>
+      </c>
+      <c r="E44" s="3">
         <v>91700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>82700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>89100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>94200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>91800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>93100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>95900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>93300</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3045700</v>
+      </c>
+      <c r="E45" s="3">
         <v>3335100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2863000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2900600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3022800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2739500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2595300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2617700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2614700</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>43684100</v>
+      </c>
+      <c r="E46" s="3">
         <v>46285100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>39280100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>39191800</v>
       </c>
-      <c r="G46" s="3">
-        <v>38255900</v>
-      </c>
       <c r="H46" s="3">
+        <v>37708800</v>
+      </c>
+      <c r="I46" s="3">
         <v>38671800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>39033300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>39897200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>38674500</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>46834800</v>
+      </c>
+      <c r="E47" s="3">
         <v>48706600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>45288100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>46330000</v>
       </c>
-      <c r="G47" s="3">
-        <v>47099900</v>
-      </c>
       <c r="H47" s="3">
+        <v>47666900</v>
+      </c>
+      <c r="I47" s="3">
         <v>45268200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>44561000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>45532800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>44251700</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>836300</v>
+      </c>
+      <c r="E48" s="3">
         <v>896800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>827400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>825400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>860000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>806200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>824900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>888500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>757700</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1564000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1635100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1523300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1549600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1604800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1554200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1548200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1541400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1540400</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1815,8 +1928,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1844,37 +1960,43 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1570900</v>
+      </c>
+      <c r="E52" s="3">
         <v>1767000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1597000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1559400</v>
       </c>
-      <c r="G52" s="3">
-        <v>1511500</v>
-      </c>
       <c r="H52" s="3">
+        <v>1491400</v>
+      </c>
+      <c r="I52" s="3">
         <v>320000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>362200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>344900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1993200</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1902,37 +2024,43 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>240494300</v>
+      </c>
+      <c r="E54" s="3">
         <v>254833800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>225480500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>223835600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>224016300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>213298700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>211587800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>217457800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>216468100</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1944,8 +2072,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1957,182 +2086,201 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>175659600</v>
+      </c>
+      <c r="E57" s="3">
         <v>184145700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>160289400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>160078100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>159974900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>151511500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>148920600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>155940200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>156235700</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>16330500</v>
+      </c>
+      <c r="E58" s="3">
         <v>17403700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>17696200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>17167900</v>
       </c>
-      <c r="G58" s="3">
-        <v>18264900</v>
-      </c>
       <c r="H58" s="3">
+        <v>17441700</v>
+      </c>
+      <c r="I58" s="3">
         <v>10739600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>9363200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>8466900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>13444100</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>337500</v>
+      </c>
+      <c r="E59" s="3">
         <v>414700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>318400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>362500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>299200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>325200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>350100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>292200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>498500</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>193355300</v>
+      </c>
+      <c r="E60" s="3">
         <v>204422500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>179890700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>179244800</v>
       </c>
-      <c r="G60" s="3">
-        <v>179629600</v>
-      </c>
       <c r="H60" s="3">
+        <v>178806400</v>
+      </c>
+      <c r="I60" s="3">
         <v>164068100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>160150100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>166235900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>171665800</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8211600</v>
+      </c>
+      <c r="E61" s="3">
         <v>9036700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8464400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8021200</v>
       </c>
-      <c r="G61" s="3">
-        <v>7266500</v>
-      </c>
       <c r="H61" s="3">
+        <v>8089700</v>
+      </c>
+      <c r="I61" s="3">
         <v>14627900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>16386700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>15550100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8818600</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>16899600</v>
+      </c>
+      <c r="E62" s="3">
         <v>18337200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>16047400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>15807700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>15570700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>14294900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>14805000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>15291300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>15580200</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2160,8 +2308,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2189,8 +2340,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2218,37 +2372,43 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>218754000</v>
+      </c>
+      <c r="E66" s="3">
         <v>232102400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>204667000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>203326400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>202730600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>193233200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>191588200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>197302000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>196237000</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2260,8 +2420,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2289,8 +2450,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2318,8 +2482,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2347,8 +2514,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2376,37 +2546,43 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8359400</v>
+      </c>
+      <c r="E72" s="3">
         <v>8452600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7590200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7043900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7538300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6955200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7238600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7121900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7384700</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2434,8 +2610,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2463,8 +2642,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2492,37 +2674,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>21016400</v>
+      </c>
+      <c r="E76" s="3">
         <v>21981300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>20167500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>19848800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>20630300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>19397800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19338300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19450300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19576800</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2550,42 +2738,48 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2613,8 +2807,11 @@
       <c r="K81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2626,37 +2823,41 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>50100</v>
+      </c>
+      <c r="E83" s="3">
         <v>48000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>48400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>49600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>10400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>45800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>41200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>41600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>-7100</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2684,8 +2885,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2713,8 +2917,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2742,8 +2949,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2771,8 +2981,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2800,37 +3013,43 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>422000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-885500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3085200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2406600</v>
       </c>
-      <c r="G89" s="3">
-        <v>-2993200</v>
-      </c>
       <c r="H89" s="3">
+        <v>-2997600</v>
+      </c>
+      <c r="I89" s="3">
         <v>-3494500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2706900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1497600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1254800</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2842,37 +3061,41 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-18600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-27400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-9700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-43300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-12800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-17300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-21700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-27600</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2900,8 +3123,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2929,37 +3155,43 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-55600</v>
+      </c>
+      <c r="E94" s="3">
         <v>44300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-28300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-19600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-72000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-24900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-25300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-28600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-51100</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2971,37 +3203,41 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>848900</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>791900</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>744600</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>819000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>765200</v>
       </c>
     </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3029,8 +3265,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3058,8 +3297,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3087,91 +3329,103 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3303800</v>
+      </c>
+      <c r="E100" s="3">
         <v>3000300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>713300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3801300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>4901500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2195400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-614800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-794800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-924000</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-8700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>153400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>24900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-111100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>107900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>95900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>21600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3918300</v>
+      </c>
+      <c r="E102" s="3">
         <v>1629200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2418700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1457400</v>
       </c>
-      <c r="G102" s="3">
-        <v>1819500</v>
-      </c>
       <c r="H102" s="3">
+        <v>1815100</v>
+      </c>
+      <c r="I102" s="3">
         <v>-1332700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3193700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>699000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>168700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MLYBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MLYBY_QTR_FIN.xlsx
@@ -1649,7 +1649,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>24272900</v>
+        <v>25605300</v>
       </c>
       <c r="E42" s="3">
         <v>24300200</v>
@@ -1661,7 +1661,7 @@
         <v>21920100</v>
       </c>
       <c r="H42" s="3">
-        <v>22193500</v>
+        <v>22740500</v>
       </c>
       <c r="I42" s="3">
         <v>19915800</v>
@@ -1777,7 +1777,7 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>43684100</v>
+        <v>45016500</v>
       </c>
       <c r="E46" s="3">
         <v>46285100</v>
@@ -1789,7 +1789,7 @@
         <v>39191800</v>
       </c>
       <c r="H46" s="3">
-        <v>37708800</v>
+        <v>38255900</v>
       </c>
       <c r="I46" s="3">
         <v>38671800</v>
@@ -1809,7 +1809,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>46834800</v>
+        <v>45493400</v>
       </c>
       <c r="E47" s="3">
         <v>48706600</v>
@@ -1821,7 +1821,7 @@
         <v>46330000</v>
       </c>
       <c r="H47" s="3">
-        <v>47666900</v>
+        <v>47099900</v>
       </c>
       <c r="I47" s="3">
         <v>45268200</v>
@@ -1969,7 +1969,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1570900</v>
+        <v>1579900</v>
       </c>
       <c r="E52" s="3">
         <v>1767000</v>
@@ -1981,7 +1981,7 @@
         <v>1559400</v>
       </c>
       <c r="H52" s="3">
-        <v>1491400</v>
+        <v>1511500</v>
       </c>
       <c r="I52" s="3">
         <v>320000</v>
@@ -2125,7 +2125,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>16330500</v>
+        <v>16958000</v>
       </c>
       <c r="E58" s="3">
         <v>17403700</v>
@@ -2137,7 +2137,7 @@
         <v>17167900</v>
       </c>
       <c r="H58" s="3">
-        <v>17441700</v>
+        <v>18264900</v>
       </c>
       <c r="I58" s="3">
         <v>10739600</v>
@@ -2189,7 +2189,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>193355300</v>
+        <v>193982800</v>
       </c>
       <c r="E60" s="3">
         <v>204422500</v>
@@ -2201,7 +2201,7 @@
         <v>179244800</v>
       </c>
       <c r="H60" s="3">
-        <v>178806400</v>
+        <v>179629600</v>
       </c>
       <c r="I60" s="3">
         <v>164068100</v>
@@ -2221,7 +2221,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8211600</v>
+        <v>7584100</v>
       </c>
       <c r="E61" s="3">
         <v>9036700</v>
@@ -2233,7 +2233,7 @@
         <v>8021200</v>
       </c>
       <c r="H61" s="3">
-        <v>8089700</v>
+        <v>7266500</v>
       </c>
       <c r="I61" s="3">
         <v>14627900</v>
@@ -2830,7 +2830,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>50100</v>
+        <v>8600</v>
       </c>
       <c r="E83" s="3">
         <v>48000</v>

--- a/AAII_Financials/Quarterly/MLYBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MLYBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="92">
   <si>
     <t>MLYBY</t>
   </si>
@@ -656,59 +656,62 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -739,8 +742,11 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -771,8 +777,11 @@
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -803,8 +812,11 @@
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -817,8 +829,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -849,8 +862,11 @@
       <c r="L12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -881,8 +897,11 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -913,8 +932,11 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -945,8 +967,11 @@
       <c r="L15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -956,8 +981,9 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -988,8 +1014,11 @@
       <c r="L17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1020,8 +1049,11 @@
       <c r="L18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1034,8 +1066,9 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1066,8 +1099,11 @@
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1098,8 +1134,11 @@
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1130,8 +1169,11 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1162,8 +1204,11 @@
       <c r="L23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1194,8 +1239,11 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1226,8 +1274,11 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1258,8 +1309,11 @@
       <c r="L26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1290,8 +1344,11 @@
       <c r="L27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1322,8 +1379,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1354,8 +1414,11 @@
       <c r="L29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1386,8 +1449,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1418,8 +1484,11 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1450,8 +1519,11 @@
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1482,8 +1554,11 @@
       <c r="L33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1514,8 +1589,11 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1546,45 +1624,51 @@
       <c r="L35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1597,8 +1681,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1611,296 +1696,324 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7595700</v>
+      </c>
+      <c r="E41" s="3">
         <v>9062800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8612800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6379400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8018100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6300600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7890400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7227400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6365400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8578500</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>22598000</v>
+      </c>
+      <c r="E42" s="3">
         <v>25605300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>24300200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>22771900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>21920100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>22740500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>19915800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>22011000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>24379500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>21721100</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5314400</v>
+      </c>
+      <c r="E43" s="3">
         <v>3133400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5903300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3578300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2736400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2300400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4297500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3409100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3278100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2296900</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>82600</v>
+      </c>
+      <c r="E44" s="3">
         <v>85100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>91700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>82700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>89100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>94200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>91800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>93100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>95900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>93300</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2971300</v>
+      </c>
+      <c r="E45" s="3">
         <v>3045700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3335100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2863000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2900600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3022800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2739500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2595300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2617700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2614700</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>42370900</v>
+      </c>
+      <c r="E46" s="3">
         <v>45016500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>46285100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>39280100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>39191800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>38255900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>38671800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>39033300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>39897200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>38674500</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>49580000</v>
+      </c>
+      <c r="E47" s="3">
         <v>45493400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>48706600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>45288100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>46330000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>47099900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>45268200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>44561000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>45532800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>44251700</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1006900</v>
+      </c>
+      <c r="E48" s="3">
         <v>836300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>896800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>827400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>825400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>860000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>806200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>824900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>888500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>757700</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1540100</v>
+      </c>
+      <c r="E49" s="3">
         <v>1564000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1635100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1523300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1549600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1604800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1554200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1548200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1541400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1540400</v>
       </c>
     </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1931,8 +2044,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1963,40 +2079,46 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1477200</v>
+      </c>
+      <c r="E52" s="3">
         <v>1579900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1767000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1597000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1559400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1511500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>320000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>362200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>344900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1993200</v>
       </c>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2027,40 +2149,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>244067100</v>
+      </c>
+      <c r="E54" s="3">
         <v>240494300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>254833800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>225480500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>223835600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>224016300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>213298700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>211587800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>217457800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>216468100</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2073,8 +2201,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2087,200 +2216,219 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>179099500</v>
+      </c>
+      <c r="E57" s="3">
         <v>175659600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>184145700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>160289400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>160078100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>159974900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>151511500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>148920600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>155940200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>156235700</v>
       </c>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>14921000</v>
+      </c>
+      <c r="E58" s="3">
         <v>16958000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>17403700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>17696200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>17167900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>18264900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10739600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>9363200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>8466900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>13444100</v>
       </c>
     </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>371200</v>
+      </c>
+      <c r="E59" s="3">
         <v>337500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>414700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>318400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>362500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>299200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>325200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>350100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>292200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>498500</v>
       </c>
     </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>196404900</v>
+      </c>
+      <c r="E60" s="3">
         <v>193982800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>204422500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>179890700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>179244800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>179629600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>164068100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>160150100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>166235900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>171665800</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8494400</v>
+      </c>
+      <c r="E61" s="3">
         <v>7584100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9036700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8464400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8021200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7266500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>14627900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>16386700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>15550100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8818600</v>
       </c>
     </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>17307300</v>
+      </c>
+      <c r="E62" s="3">
         <v>16899600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>18337200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>16047400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>15807700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>15570700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>14294900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>14805000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>15291300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>15580200</v>
       </c>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2311,8 +2459,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2343,8 +2494,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2375,40 +2529,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>222490300</v>
+      </c>
+      <c r="E66" s="3">
         <v>218754000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>232102400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>204667000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>203326400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>202730600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>193233200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>191588200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>197302000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>196237000</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2421,8 +2581,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2453,8 +2614,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2485,8 +2649,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2517,8 +2684,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2549,40 +2719,46 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8127800</v>
+      </c>
+      <c r="E72" s="3">
         <v>8359400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>8452600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7590200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7043900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7538300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6955200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7238600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7121900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7384700</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2613,8 +2789,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2645,8 +2824,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2677,40 +2859,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20835400</v>
+      </c>
+      <c r="E76" s="3">
         <v>21016400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>21981300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>20167500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>19848800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20630300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19397800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19338300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19450300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19576800</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2741,45 +2929,51 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2810,8 +3004,11 @@
       <c r="L81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2824,40 +3021,44 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>46200</v>
+      </c>
+      <c r="E83" s="3">
         <v>8600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>48000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>48400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>49600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>10400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>45800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>41200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>41600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>-7100</v>
       </c>
     </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2888,8 +3089,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2920,8 +3124,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2952,8 +3159,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2984,8 +3194,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3016,40 +3229,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3567500</v>
+      </c>
+      <c r="E89" s="3">
         <v>422000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-885500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3085200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2406600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2997600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3494500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2706900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1497600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1254800</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3062,40 +3281,44 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-31200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-18600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-27400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-43300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-12800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-17300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-21700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-27600</v>
       </c>
     </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3126,8 +3349,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3158,40 +3384,46 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-55600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>44300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-28300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-19600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-72000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-24900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-25300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-28600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-51100</v>
       </c>
     </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3204,40 +3436,44 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>870500</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>848900</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>791900</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>744600</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>819000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>765200</v>
       </c>
     </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3268,8 +3504,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3300,8 +3539,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3332,100 +3574,112 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1061300</v>
+      </c>
+      <c r="E100" s="3">
         <v>3303800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3000300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>713300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3801300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>4901500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2195400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-614800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-794800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-924000</v>
       </c>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>82200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-16800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-8700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>153400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>24900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-111100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>107900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>95900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>21600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2516500</v>
+      </c>
+      <c r="E102" s="3">
         <v>3918300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1629200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2418700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1457400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1815100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1332700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3193700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>699000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>168700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MLYBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MLYBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="92">
   <si>
     <t>MLYBY</t>
   </si>
@@ -656,68 +656,74 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -757,8 +763,14 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -798,8 +810,14 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -839,8 +857,14 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -856,8 +880,10 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -897,8 +923,14 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -938,8 +970,14 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -979,8 +1017,14 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1020,8 +1064,14 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1034,8 +1084,10 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1075,8 +1127,14 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1116,8 +1174,14 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1133,8 +1197,10 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1174,8 +1240,14 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1215,8 +1287,14 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1256,8 +1334,14 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1297,8 +1381,14 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1338,8 +1428,14 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1379,8 +1475,14 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1420,8 +1522,14 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1461,8 +1569,14 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1502,8 +1616,14 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1543,8 +1663,14 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1584,8 +1710,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1625,8 +1757,14 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1666,8 +1804,14 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1707,8 +1851,14 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1748,8 +1898,14 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1789,54 +1945,66 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1852,8 +2020,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1869,377 +2039,433 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7969600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>6977500</v>
+      </c>
+      <c r="F41" s="3">
         <v>9183000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>10901600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>7595700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>9062800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>8612800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>6379400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>8018100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>6300600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>7890400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>7227400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>6365400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>8578500</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>22747200</v>
+      </c>
+      <c r="E42" s="3">
+        <v>26189200</v>
+      </c>
+      <c r="F42" s="3">
         <v>22538300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>23992000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>22598000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>25605300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>24300200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>22771900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>21920100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>22740500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>19915800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>22011000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>24379500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>21721100</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5715900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3957500</v>
+      </c>
+      <c r="F43" s="3">
         <v>5620600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>5445600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>5314400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>3133400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>5903300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>3578300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2736400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2300400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>4297500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>3409100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>3278100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>2296900</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>68300</v>
+      </c>
+      <c r="E44" s="3">
+        <v>84200</v>
+      </c>
+      <c r="F44" s="3">
         <v>79400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>83200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>82600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>85100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>91700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>82700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>89100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>94200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>91800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>93100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>95900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>93300</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3209600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>3184900</v>
+      </c>
+      <c r="F45" s="3">
         <v>3241800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>3008800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>2971300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>3045700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>3335100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>2863000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>2900600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>3022800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>2739500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>2595300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>2617700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>2614700</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>42822500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>43562400</v>
+      </c>
+      <c r="F46" s="3">
         <v>43995500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>46566600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>42370900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>45016500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>46285100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>39280100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>39191800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>38255900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>38671800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>39033300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>39897200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>38674500</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>49299300</v>
+      </c>
+      <c r="E47" s="3">
+        <v>47452400</v>
+      </c>
+      <c r="F47" s="3">
         <v>48502500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>48156600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>49580000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>45493400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>48706600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>45288100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>46330000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>47099900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>45268200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>44561000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>45532800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>44251700</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1076400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1079400</v>
+      </c>
+      <c r="F48" s="3">
         <v>1037600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1049300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1006900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>836300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>896800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>827400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>825400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>860000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>806200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>824900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>888500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>757700</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1590100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1609000</v>
+      </c>
+      <c r="F49" s="3">
         <v>1567800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1592000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1540100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1564000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1635100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1523300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1549600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1604800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1554200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1548200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1541400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1540400</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2279,8 +2505,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2320,49 +2552,61 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1539600</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1596400</v>
+      </c>
+      <c r="F52" s="3">
         <v>1586000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>1596600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>1477200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>1579900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>1767000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1597000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1559400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1511500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>320000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>362200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>344900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1993200</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2402,49 +2646,61 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>260409700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>259509700</v>
+      </c>
+      <c r="F54" s="3">
         <v>253553400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>254780500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>244067100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>240494300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>254833800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>225480500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>223835600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>224016300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>213298700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>211587800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>217457800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>216468100</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2460,8 +2716,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2477,254 +2735,292 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>187604300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>188101100</v>
+      </c>
+      <c r="F57" s="3">
         <v>186074600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>187942400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>179099500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>175659600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>184145700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>160289400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>160078100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>159974900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>151511500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>148920600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>155940200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>156235700</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>16414500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>16004300</v>
+      </c>
+      <c r="F58" s="3">
         <v>12483800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>13497600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>14921000</v>
       </c>
-      <c r="G58" s="3">
-        <v>16958000</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
+        <v>16965700</v>
+      </c>
+      <c r="J58" s="3">
         <v>17403700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>17696200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>17167900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>18264900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>10739600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>9363200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>8466900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>13444100</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>443200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>455200</v>
+      </c>
+      <c r="F59" s="3">
         <v>474400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>455000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>371200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>337500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>414700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>318400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>362500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>299200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>325200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>350100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>292200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>498500</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>207056800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>206200100</v>
+      </c>
+      <c r="F60" s="3">
         <v>201807900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>204336700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>196404900</v>
       </c>
-      <c r="G60" s="3">
-        <v>193982800</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
+        <v>193990500</v>
+      </c>
+      <c r="J60" s="3">
         <v>204422500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>179890700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>179244800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>179629600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>164068100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>160150100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>166235900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>171665800</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10361100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>9398900</v>
+      </c>
+      <c r="F61" s="3">
         <v>9651200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>8386700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>8494400</v>
       </c>
-      <c r="G61" s="3">
-        <v>7584100</v>
-      </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
+        <v>7576400</v>
+      </c>
+      <c r="J61" s="3">
         <v>9036700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>8464400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>8021200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>7266500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>14627900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>16386700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>15550100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>8818600</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>19546900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>19748700</v>
+      </c>
+      <c r="F62" s="3">
         <v>18982400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>18612800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>17307300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>16899600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>18337200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>16047400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>15807700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>15570700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>14294900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>14805000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>15291300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>15580200</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2764,8 +3060,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2805,8 +3107,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2846,49 +3154,61 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>237245500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>235656500</v>
+      </c>
+      <c r="F66" s="3">
         <v>230750600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>231643900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>222490300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>218754000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>232102400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>204667000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>203326400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>202730600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>193233200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>191588200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>197302000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>196237000</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2904,8 +3224,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2945,8 +3267,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2986,8 +3314,14 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3027,8 +3361,14 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3068,49 +3408,61 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9598100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>9942300</v>
+      </c>
+      <c r="F72" s="3">
         <v>8947900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>9181300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>8127800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>8359400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>8452600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>7590200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>7043900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>7538300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>6955200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>7238600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>7121900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>7384700</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3150,8 +3502,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3191,8 +3549,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3232,49 +3596,61 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>22312000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>23016500</v>
+      </c>
+      <c r="F76" s="3">
         <v>22013300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>22356100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>20835400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>21016400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>21981300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>20167500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>19848800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>20630300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>19397800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>19338300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>19450300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>19576800</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3314,54 +3690,66 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3401,8 +3789,14 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3418,49 +3812,57 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>46200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F83" s="3">
         <v>50000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>45900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>46200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>8600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>48000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>48400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>49600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>10400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>45800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>41200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>41600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>-7100</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3500,8 +3902,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3541,8 +3949,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3582,8 +3996,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3623,8 +4043,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3664,49 +4090,61 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-389100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>240700</v>
+      </c>
+      <c r="F89" s="3">
         <v>-2730600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>3744400</v>
       </c>
-      <c r="F89" s="3">
-        <v>-3567500</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
+        <v>-3573300</v>
+      </c>
+      <c r="I89" s="3">
         <v>422000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-885500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-3085200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-2406600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-2997600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-3494500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-2706900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1497600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>1254800</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3722,49 +4160,57 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-38200</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-55800</v>
+      </c>
+      <c r="F91" s="3">
         <v>-29100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-34000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-16600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-31200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-18600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-27400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-9700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-43300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-12800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-17300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-21700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-27600</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3804,8 +4250,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3845,49 +4297,61 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-33600</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-101000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-34100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-27800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-11100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-55600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>44300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-28300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-19600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-72000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-24900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-25300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-28600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-51100</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3903,49 +4367,57 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>984600</v>
+      </c>
+      <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>860900</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>870500</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>848900</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>791900</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>744600</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>819000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>765200</v>
       </c>
     </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3985,8 +4457,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4026,8 +4504,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4067,127 +4551,151 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-603400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-1482300</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1315100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-160500</v>
       </c>
-      <c r="F100" s="3">
-        <v>1061300</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
+        <v>1067100</v>
+      </c>
+      <c r="I100" s="3">
         <v>3303800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>3000300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>713300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>3801300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>4901500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>2195400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-614800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-794800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-924000</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>800</v>
+      </c>
+      <c r="E101" s="3">
+        <v>248100</v>
+      </c>
+      <c r="F101" s="3">
         <v>-529900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-18400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>82200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-16800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-8700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>153400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>24900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-111100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>107900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>95900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>21600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1048500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1517300</v>
+      </c>
+      <c r="F102" s="3">
         <v>-4112900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>3428400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-2516500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>3918300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>1629200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-2418700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>1457400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>1815100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-1332700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-3193700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>699000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>168700</v>
       </c>
     </row>
